--- a/media/Levels/Level_7.xlsx
+++ b/media/Levels/Level_7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CCB5166F-390C-4D95-88EB-C58CB1C5049B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACE975D-B86C-4091-A8FA-4CCF754A2F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -1086,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="BX3" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CY3" s="3">
         <v>9</v>
@@ -1488,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="BX6" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CV6" s="3">
         <v>9</v>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="BX9" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CK9" s="1">
         <v>4</v>
@@ -3753,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="BX21" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CK21" s="1">
         <v>4</v>
@@ -3900,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="BX24" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CK24" s="1">
         <v>4</v>
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="BX27" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CK27" s="1">
         <v>4</v>
@@ -4044,7 +4044,7 @@
         <v>0</v>
       </c>
       <c r="BX30" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CK30" s="1">
         <v>4</v>
@@ -11489,7 +11489,7 @@
         <v>0</v>
       </c>
       <c r="BX121" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="DD121" s="4">
         <v>0</v>
@@ -11828,7 +11828,7 @@
         <v>0</v>
       </c>
       <c r="BX124" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CR124" s="4">
         <v>0</v>
@@ -12245,7 +12245,7 @@
         <v>0</v>
       </c>
       <c r="BX127" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CR127" s="4">
         <v>0</v>
@@ -12677,7 +12677,7 @@
         <v>0</v>
       </c>
       <c r="BX130" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="DO130" s="2">
         <v>0</v>
@@ -14543,7 +14543,7 @@
         <v>0</v>
       </c>
       <c r="BX145" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CI145" s="4">
         <v>0</v>
@@ -14591,7 +14591,7 @@
         <v>0</v>
       </c>
       <c r="BX148" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="EQ148" s="1">
         <v>0</v>

--- a/media/Levels/Level_7.xlsx
+++ b/media/Levels/Level_7.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACE975D-B86C-4091-A8FA-4CCF754A2F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E3D2693-267E-4359-B4A1-8BCB4F173063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Level_7" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4101,26 +4101,29 @@
       <c r="AE32" s="4">
         <v>0</v>
       </c>
+      <c r="BH32" s="1">
+        <v>0</v>
+      </c>
       <c r="BI32" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ32" s="1">
         <v>0</v>
       </c>
       <c r="BK32" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL32" s="1">
         <v>3</v>
       </c>
-      <c r="BL32" s="1">
-        <v>0</v>
-      </c>
       <c r="BM32" s="1">
         <v>0</v>
       </c>
       <c r="BN32" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO32" s="1">
         <v>3</v>
-      </c>
-      <c r="BO32" s="1">
-        <v>0</v>
       </c>
       <c r="BP32" s="1">
         <v>0</v>
@@ -4174,24 +4177,27 @@
         <v>0</v>
       </c>
       <c r="CG32" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CH32" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI32" s="1">
+        <v>0</v>
+      </c>
+      <c r="CJ32" s="1">
         <v>3</v>
       </c>
-      <c r="CI32" s="1">
-        <v>0</v>
-      </c>
-      <c r="CJ32" s="1">
-        <v>0</v>
-      </c>
       <c r="CK32" s="1">
+        <v>0</v>
+      </c>
+      <c r="CL32" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM32" s="1">
         <v>3</v>
       </c>
-      <c r="CL32" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM32" s="1">
+      <c r="CN32" s="1">
         <v>0</v>
       </c>
       <c r="ET32" s="1">
@@ -4203,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="BJ33" s="1">
-        <v>6</v>
-      </c>
-      <c r="BV33" s="3">
-        <v>0</v>
-      </c>
-      <c r="BZ33" s="3">
+        <v>0</v>
+      </c>
+      <c r="BU33" s="3">
+        <v>0</v>
+      </c>
+      <c r="CA33" s="3">
         <v>0</v>
       </c>
       <c r="CL33" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="ET33" s="1">
         <v>0</v>
@@ -4222,17 +4228,20 @@
       <c r="A34" s="1">
         <v>0</v>
       </c>
+      <c r="AP34" s="1">
+        <v>0</v>
+      </c>
       <c r="BK34" s="1">
-        <v>0</v>
-      </c>
-      <c r="BU34" s="3">
+        <v>6</v>
+      </c>
+      <c r="BT34" s="3">
         <v>9</v>
       </c>
-      <c r="CA34" s="3">
+      <c r="CB34" s="3">
         <v>10</v>
       </c>
       <c r="CK34" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="ET34" s="1">
         <v>0</v>
@@ -4242,16 +4251,16 @@
       <c r="A35" s="1">
         <v>0</v>
       </c>
-      <c r="AP35" s="1">
-        <v>0</v>
+      <c r="AQ35" s="1">
+        <v>6</v>
       </c>
       <c r="BL35" s="1">
         <v>0</v>
       </c>
-      <c r="BT35" s="3">
-        <v>0</v>
-      </c>
-      <c r="CB35" s="3">
+      <c r="BS35" s="3">
+        <v>0</v>
+      </c>
+      <c r="CC35" s="3">
         <v>0</v>
       </c>
       <c r="CJ35" s="1">
@@ -4265,20 +4274,20 @@
       <c r="A36" s="1">
         <v>0</v>
       </c>
-      <c r="AQ36" s="1">
-        <v>6</v>
+      <c r="AR36" s="1">
+        <v>0</v>
       </c>
       <c r="BM36" s="1">
-        <v>6</v>
-      </c>
-      <c r="BS36" s="3">
-        <v>0</v>
-      </c>
-      <c r="CC36" s="3">
+        <v>0</v>
+      </c>
+      <c r="BR36" s="3">
+        <v>0</v>
+      </c>
+      <c r="CD36" s="3">
         <v>0</v>
       </c>
       <c r="CI36" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="ET36" s="1">
         <v>0</v>
@@ -4288,20 +4297,20 @@
       <c r="A37" s="1">
         <v>0</v>
       </c>
-      <c r="AR37" s="1">
+      <c r="AS37" s="1">
         <v>0</v>
       </c>
       <c r="BN37" s="1">
-        <v>0</v>
-      </c>
-      <c r="BR37" s="3">
+        <v>6</v>
+      </c>
+      <c r="BQ37" s="3">
         <v>9</v>
       </c>
-      <c r="CD37" s="3">
+      <c r="CE37" s="3">
         <v>10</v>
       </c>
       <c r="CH37" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="ET37" s="1">
         <v>0</v>
@@ -4311,16 +4320,16 @@
       <c r="A38" s="1">
         <v>0</v>
       </c>
-      <c r="AS38" s="1">
-        <v>0</v>
+      <c r="AT38" s="1">
+        <v>6</v>
       </c>
       <c r="BO38" s="1">
         <v>0</v>
       </c>
-      <c r="BQ38" s="3">
-        <v>0</v>
-      </c>
-      <c r="CE38" s="3">
+      <c r="BP38" s="3">
+        <v>0</v>
+      </c>
+      <c r="CF38" s="3">
         <v>0</v>
       </c>
       <c r="CG38" s="1">
@@ -4394,14 +4403,92 @@
       <c r="A39" s="1">
         <v>0</v>
       </c>
-      <c r="AT39" s="1">
-        <v>6</v>
+      <c r="AU39" s="1">
+        <v>0</v>
+      </c>
+      <c r="BA39" s="1">
+        <v>0</v>
+      </c>
+      <c r="BB39" s="1">
+        <v>0</v>
+      </c>
+      <c r="BC39" s="1">
+        <v>3</v>
+      </c>
+      <c r="BD39" s="1">
+        <v>0</v>
+      </c>
+      <c r="BE39" s="1">
+        <v>0</v>
+      </c>
+      <c r="BF39" s="1">
+        <v>3</v>
+      </c>
+      <c r="BG39" s="1">
+        <v>0</v>
+      </c>
+      <c r="BH39" s="1">
+        <v>0</v>
+      </c>
+      <c r="BI39" s="1">
+        <v>3</v>
+      </c>
+      <c r="BJ39" s="1">
+        <v>0</v>
+      </c>
+      <c r="BK39" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL39" s="1">
+        <v>3</v>
+      </c>
+      <c r="BM39" s="1">
+        <v>0</v>
+      </c>
+      <c r="BN39" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO39" s="1">
+        <v>3</v>
       </c>
       <c r="BP39" s="1">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="CE39" s="1">
+        <v>0</v>
       </c>
       <c r="CF39" s="1">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="CG39" s="1">
+        <v>0</v>
+      </c>
+      <c r="CH39" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI39" s="1">
+        <v>3</v>
+      </c>
+      <c r="CJ39" s="1">
+        <v>0</v>
+      </c>
+      <c r="CK39" s="1">
+        <v>0</v>
+      </c>
+      <c r="CL39" s="1">
+        <v>3</v>
+      </c>
+      <c r="CM39" s="1">
+        <v>0</v>
+      </c>
+      <c r="CN39" s="1">
+        <v>0</v>
+      </c>
+      <c r="CO39" s="1">
+        <v>3</v>
+      </c>
+      <c r="CP39" s="1">
+        <v>0</v>
       </c>
       <c r="CQ39" s="2">
         <v>0</v>
@@ -4471,59 +4558,11 @@
       <c r="A40" s="1">
         <v>0</v>
       </c>
-      <c r="AU40" s="1">
-        <v>0</v>
-      </c>
-      <c r="BA40" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB40" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC40" s="1">
-        <v>3</v>
-      </c>
-      <c r="BD40" s="1">
-        <v>0</v>
-      </c>
-      <c r="BE40" s="1">
-        <v>0</v>
-      </c>
-      <c r="BF40" s="1">
-        <v>3</v>
-      </c>
-      <c r="BG40" s="1">
-        <v>0</v>
-      </c>
-      <c r="BH40" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI40" s="1">
-        <v>3</v>
-      </c>
-      <c r="BJ40" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK40" s="1">
-        <v>0</v>
-      </c>
-      <c r="BL40" s="1">
-        <v>3</v>
-      </c>
-      <c r="BM40" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN40" s="1">
-        <v>0</v>
-      </c>
-      <c r="BO40" s="1">
-        <v>3</v>
-      </c>
-      <c r="BP40" s="1">
-        <v>0</v>
-      </c>
-      <c r="CE40" s="1">
-        <v>0</v>
+      <c r="AV40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AZ40" s="1">
+        <v>5</v>
       </c>
       <c r="CQ40" s="2">
         <v>0</v>
@@ -4593,46 +4632,10 @@
       <c r="A41" s="1">
         <v>0</v>
       </c>
-      <c r="AV41" s="1">
-        <v>0</v>
-      </c>
-      <c r="AZ41" s="1">
-        <v>5</v>
-      </c>
-      <c r="CE41" s="1">
-        <v>0</v>
-      </c>
-      <c r="CF41" s="1">
-        <v>3</v>
-      </c>
-      <c r="CG41" s="1">
-        <v>0</v>
-      </c>
-      <c r="CH41" s="1">
-        <v>0</v>
-      </c>
-      <c r="CI41" s="1">
-        <v>3</v>
-      </c>
-      <c r="CJ41" s="1">
-        <v>0</v>
-      </c>
-      <c r="CK41" s="1">
-        <v>0</v>
-      </c>
-      <c r="CL41" s="1">
-        <v>3</v>
-      </c>
-      <c r="CM41" s="1">
-        <v>0</v>
-      </c>
-      <c r="CN41" s="1">
-        <v>0</v>
-      </c>
-      <c r="CO41" s="1">
-        <v>3</v>
-      </c>
-      <c r="CP41" s="1">
+      <c r="AW41" s="1">
+        <v>6</v>
+      </c>
+      <c r="AY41" s="1">
         <v>0</v>
       </c>
       <c r="CQ41" s="2">
@@ -4703,10 +4706,7 @@
       <c r="A42" s="1">
         <v>0</v>
       </c>
-      <c r="AW42" s="1">
-        <v>6</v>
-      </c>
-      <c r="AY42" s="1">
+      <c r="AX42" s="1">
         <v>0</v>
       </c>
       <c r="CQ42" s="2">
@@ -4778,9 +4778,6 @@
         <v>0</v>
       </c>
       <c r="AB43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AX43" s="1">
         <v>0</v>
       </c>
       <c r="CQ43" s="2">
@@ -7674,7 +7671,7 @@
         <v>0</v>
       </c>
       <c r="C75" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
@@ -7683,7 +7680,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G75" s="2">
         <v>0</v>
@@ -7815,7 +7812,7 @@
         <v>0</v>
       </c>
       <c r="DQ75" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DR75" s="1">
         <v>0</v>
@@ -7824,7 +7821,7 @@
         <v>0</v>
       </c>
       <c r="DT75" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="DU75" s="1">
         <v>0</v>
@@ -7839,7 +7836,7 @@
         <v>0</v>
       </c>
       <c r="EO75" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="EP75" s="1">
         <v>0</v>
@@ -7848,7 +7845,7 @@
         <v>0</v>
       </c>
       <c r="ER75" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="ES75" s="1">
         <v>0</v>

--- a/media/Levels/Level_7.xlsx
+++ b/media/Levels/Level_7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3E3D2693-267E-4359-B4A1-8BCB4F173063}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65279156-F4B9-4775-B110-200D5AC8BB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -131,6 +131,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF6E01"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -10131,9 +10136,6 @@
       <c r="K101" s="3">
         <v>8</v>
       </c>
-      <c r="Z101" s="4">
-        <v>0</v>
-      </c>
       <c r="AA101" s="4">
         <v>0</v>
       </c>
@@ -10144,6 +10146,9 @@
         <v>0</v>
       </c>
       <c r="AD101" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="4">
         <v>0</v>
       </c>
       <c r="AQ101" s="4">
@@ -10190,9 +10195,6 @@
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="Z102" s="4">
-        <v>0</v>
-      </c>
       <c r="AA102" s="4">
         <v>0</v>
       </c>
@@ -10203,6 +10205,9 @@
         <v>0</v>
       </c>
       <c r="AD102" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="4">
         <v>0</v>
       </c>
       <c r="AQ102" s="4">
@@ -10264,19 +10269,19 @@
       <c r="K103" s="3">
         <v>0</v>
       </c>
-      <c r="Z103" s="4">
-        <v>0</v>
-      </c>
       <c r="AA103" s="4">
         <v>0</v>
       </c>
       <c r="AB103" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC103" s="4">
         <v>11</v>
       </c>
-      <c r="AC103" s="4">
-        <v>0</v>
-      </c>
       <c r="AD103" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE103" s="4">
         <v>0</v>
       </c>
       <c r="AQ103" s="4">
@@ -10353,9 +10358,6 @@
       <c r="K104" s="3">
         <v>8</v>
       </c>
-      <c r="Z104" s="4">
-        <v>0</v>
-      </c>
       <c r="AA104" s="4">
         <v>0</v>
       </c>
@@ -10366,6 +10368,9 @@
         <v>0</v>
       </c>
       <c r="AD104" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE104" s="4">
         <v>0</v>
       </c>
       <c r="AQ104" s="4">
@@ -10442,9 +10447,6 @@
       <c r="K105" s="3">
         <v>0</v>
       </c>
-      <c r="Z105" s="4">
-        <v>0</v>
-      </c>
       <c r="AA105" s="4">
         <v>0</v>
       </c>
@@ -10455,6 +10457,9 @@
         <v>0</v>
       </c>
       <c r="AD105" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE105" s="4">
         <v>0</v>
       </c>
       <c r="AQ105" s="4">
@@ -10516,6 +10521,9 @@
       <c r="K106" s="3">
         <v>0</v>
       </c>
+      <c r="Z106" s="4">
+        <v>0</v>
+      </c>
       <c r="AA106" s="4">
         <v>0</v>
       </c>
@@ -10526,9 +10534,6 @@
         <v>0</v>
       </c>
       <c r="AD106" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE106" s="4">
         <v>0</v>
       </c>
       <c r="AV106" s="4">
@@ -10575,6 +10580,9 @@
       <c r="K107" s="3">
         <v>8</v>
       </c>
+      <c r="Z107" s="4">
+        <v>0</v>
+      </c>
       <c r="AA107" s="4">
         <v>0</v>
       </c>
@@ -10585,9 +10593,6 @@
         <v>0</v>
       </c>
       <c r="AD107" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE107" s="4">
         <v>0</v>
       </c>
       <c r="AV107" s="4">
@@ -10619,19 +10624,19 @@
       <c r="K108" s="3">
         <v>0</v>
       </c>
+      <c r="Z108" s="4">
+        <v>0</v>
+      </c>
       <c r="AA108" s="4">
         <v>0</v>
       </c>
       <c r="AB108" s="4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC108" s="4">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD108" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE108" s="4">
         <v>0</v>
       </c>
       <c r="AX108" s="4">
@@ -10663,6 +10668,9 @@
       <c r="K109" s="1">
         <v>0</v>
       </c>
+      <c r="Z109" s="4">
+        <v>0</v>
+      </c>
       <c r="AA109" s="4">
         <v>0</v>
       </c>
@@ -10673,9 +10681,6 @@
         <v>0</v>
       </c>
       <c r="AD109" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE109" s="4">
         <v>0</v>
       </c>
       <c r="AX109" s="4">
@@ -10707,6 +10712,9 @@
       <c r="K110" s="1">
         <v>4</v>
       </c>
+      <c r="Z110" s="4">
+        <v>0</v>
+      </c>
       <c r="AA110" s="4">
         <v>0</v>
       </c>
@@ -10717,9 +10725,6 @@
         <v>0</v>
       </c>
       <c r="AD110" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE110" s="4">
         <v>0</v>
       </c>
       <c r="AX110" s="4">
@@ -10780,6 +10785,12 @@
         <v>3</v>
       </c>
       <c r="BQ110" s="1">
+        <v>0</v>
+      </c>
+      <c r="BR110" s="1">
+        <v>0</v>
+      </c>
+      <c r="CD110" s="1">
         <v>0</v>
       </c>
       <c r="CE110" s="1">
@@ -10890,10 +10901,10 @@
         <v>0</v>
       </c>
       <c r="BQ111" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CE111" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="ET111" s="1">
         <v>0</v>
@@ -10937,10 +10948,10 @@
         <v>0</v>
       </c>
       <c r="BP112" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CF112" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="ET112" s="1">
         <v>0</v>
@@ -11001,10 +11012,10 @@
         <v>0</v>
       </c>
       <c r="BN114" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CH114" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="ET114" s="1">
         <v>0</v>
@@ -11033,10 +11044,10 @@
         <v>0</v>
       </c>
       <c r="BM115" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CI115" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="ET115" s="1">
         <v>0</v>
@@ -11097,10 +11108,10 @@
         <v>0</v>
       </c>
       <c r="BK117" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CK117" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="ET117" s="1">
         <v>0</v>
@@ -11129,10 +11140,10 @@
         <v>0</v>
       </c>
       <c r="BJ118" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CL118" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="DD118" s="4">
         <v>0</v>
@@ -11175,26 +11186,29 @@
       <c r="AE119" s="4">
         <v>0</v>
       </c>
+      <c r="BH119" s="1">
+        <v>0</v>
+      </c>
       <c r="BI119" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BJ119" s="1">
         <v>0</v>
       </c>
       <c r="BK119" s="1">
+        <v>0</v>
+      </c>
+      <c r="BL119" s="1">
         <v>3</v>
       </c>
-      <c r="BL119" s="1">
-        <v>0</v>
-      </c>
       <c r="BM119" s="1">
         <v>0</v>
       </c>
       <c r="BN119" s="1">
+        <v>0</v>
+      </c>
+      <c r="BO119" s="1">
         <v>3</v>
-      </c>
-      <c r="BO119" s="1">
-        <v>0</v>
       </c>
       <c r="BP119" s="1">
         <v>0</v>
@@ -11248,24 +11262,27 @@
         <v>0</v>
       </c>
       <c r="CG119" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CH119" s="1">
+        <v>0</v>
+      </c>
+      <c r="CI119" s="1">
+        <v>0</v>
+      </c>
+      <c r="CJ119" s="1">
         <v>3</v>
       </c>
-      <c r="CI119" s="1">
-        <v>0</v>
-      </c>
-      <c r="CJ119" s="1">
-        <v>0</v>
-      </c>
       <c r="CK119" s="1">
+        <v>0</v>
+      </c>
+      <c r="CL119" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM119" s="1">
         <v>3</v>
       </c>
-      <c r="CL119" s="1">
-        <v>0</v>
-      </c>
-      <c r="CM119" s="1">
+      <c r="CN119" s="1">
         <v>0</v>
       </c>
       <c r="DD119" s="4">
@@ -11470,19 +11487,7 @@
       <c r="M121" s="4">
         <v>0</v>
       </c>
-      <c r="AC121" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD121" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE121" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF121" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG121" s="4">
+      <c r="AC121" s="1">
         <v>0</v>
       </c>
       <c r="BX121" s="1">
@@ -11586,20 +11591,8 @@
       <c r="M122" s="4">
         <v>0</v>
       </c>
-      <c r="AC122" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD122" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE122" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF122" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG122" s="4">
-        <v>0</v>
+      <c r="AD122" s="1">
+        <v>6</v>
       </c>
       <c r="BX122" s="1">
         <v>0</v>
@@ -11705,19 +11698,7 @@
       <c r="N123" s="1">
         <v>6</v>
       </c>
-      <c r="AC123" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD123" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE123" s="4">
-        <v>11</v>
-      </c>
-      <c r="AF123" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG123" s="4">
+      <c r="AE123" s="1">
         <v>0</v>
       </c>
       <c r="BX123" s="1">
@@ -11809,19 +11790,7 @@
       <c r="O124" s="1">
         <v>0</v>
       </c>
-      <c r="AC124" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD124" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE124" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF124" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG124" s="4">
+      <c r="AF124" s="1">
         <v>0</v>
       </c>
       <c r="BX124" s="1">
@@ -11928,20 +11897,8 @@
       <c r="P125" s="1">
         <v>0</v>
       </c>
-      <c r="AC125" s="4">
-        <v>0</v>
-      </c>
-      <c r="AD125" s="4">
-        <v>0</v>
-      </c>
-      <c r="AE125" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF125" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG125" s="4">
-        <v>0</v>
+      <c r="AG125" s="1">
+        <v>6</v>
       </c>
       <c r="BX125" s="1">
         <v>0</v>

--- a/media/Levels/Level_7.xlsx
+++ b/media/Levels/Level_7.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\OneDrive - 学校法人新潟総合学院 学校法人国際総合学園 学校法人大彦学園\デスクトップ\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65279156-F4B9-4775-B110-200D5AC8BB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23193D26-87EA-402F-BE8E-250E5D3E12B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -4459,41 +4459,38 @@
       <c r="BP39" s="1">
         <v>0</v>
       </c>
-      <c r="CE39" s="1">
-        <v>0</v>
-      </c>
       <c r="CF39" s="1">
+        <v>0</v>
+      </c>
+      <c r="CG39" s="1">
         <v>3</v>
       </c>
-      <c r="CG39" s="1">
-        <v>0</v>
-      </c>
       <c r="CH39" s="1">
         <v>0</v>
       </c>
       <c r="CI39" s="1">
+        <v>0</v>
+      </c>
+      <c r="CJ39" s="1">
         <v>3</v>
       </c>
-      <c r="CJ39" s="1">
-        <v>0</v>
-      </c>
       <c r="CK39" s="1">
         <v>0</v>
       </c>
       <c r="CL39" s="1">
+        <v>0</v>
+      </c>
+      <c r="CM39" s="1">
         <v>3</v>
       </c>
-      <c r="CM39" s="1">
-        <v>0</v>
-      </c>
       <c r="CN39" s="1">
         <v>0</v>
       </c>
       <c r="CO39" s="1">
+        <v>0</v>
+      </c>
+      <c r="CP39" s="1">
         <v>3</v>
-      </c>
-      <c r="CP39" s="1">
-        <v>0</v>
       </c>
       <c r="CQ39" s="2">
         <v>0</v>

--- a/media/Levels/Level_7.xlsx
+++ b/media/Levels/Level_7.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23193D26-87EA-402F-BE8E-250E5D3E12B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D603D78-3AF2-4EC9-8852-E59B9BB50817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -4205,6 +4205,66 @@
       <c r="CN32" s="1">
         <v>0</v>
       </c>
+      <c r="CQ32" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR32" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS32" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT32" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU32" s="2">
+        <v>0</v>
+      </c>
+      <c r="CV32" s="2">
+        <v>0</v>
+      </c>
+      <c r="CW32" s="2">
+        <v>0</v>
+      </c>
+      <c r="CX32" s="2">
+        <v>0</v>
+      </c>
+      <c r="CY32" s="2">
+        <v>0</v>
+      </c>
+      <c r="CZ32" s="2">
+        <v>0</v>
+      </c>
+      <c r="DA32" s="2">
+        <v>0</v>
+      </c>
+      <c r="DB32" s="2">
+        <v>0</v>
+      </c>
+      <c r="DC32" s="2">
+        <v>0</v>
+      </c>
+      <c r="DD32" s="2">
+        <v>0</v>
+      </c>
+      <c r="DE32" s="2">
+        <v>0</v>
+      </c>
+      <c r="DF32" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG32" s="2">
+        <v>0</v>
+      </c>
+      <c r="DH32" s="2">
+        <v>0</v>
+      </c>
+      <c r="DI32" s="2">
+        <v>0</v>
+      </c>
+      <c r="DJ32" s="2">
+        <v>0</v>
+      </c>
       <c r="ET32" s="1">
         <v>0</v>
       </c>
@@ -4225,6 +4285,66 @@
       <c r="CL33" s="1">
         <v>0</v>
       </c>
+      <c r="CQ33" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR33" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS33" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT33" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU33" s="2">
+        <v>0</v>
+      </c>
+      <c r="CV33" s="2">
+        <v>0</v>
+      </c>
+      <c r="CW33" s="2">
+        <v>0</v>
+      </c>
+      <c r="CX33" s="2">
+        <v>0</v>
+      </c>
+      <c r="CY33" s="2">
+        <v>0</v>
+      </c>
+      <c r="CZ33" s="2">
+        <v>0</v>
+      </c>
+      <c r="DA33" s="2">
+        <v>0</v>
+      </c>
+      <c r="DB33" s="2">
+        <v>0</v>
+      </c>
+      <c r="DC33" s="2">
+        <v>0</v>
+      </c>
+      <c r="DD33" s="2">
+        <v>0</v>
+      </c>
+      <c r="DE33" s="2">
+        <v>0</v>
+      </c>
+      <c r="DF33" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG33" s="2">
+        <v>0</v>
+      </c>
+      <c r="DH33" s="2">
+        <v>0</v>
+      </c>
+      <c r="DI33" s="2">
+        <v>0</v>
+      </c>
+      <c r="DJ33" s="2">
+        <v>0</v>
+      </c>
       <c r="ET33" s="1">
         <v>0</v>
       </c>
@@ -4248,6 +4368,66 @@
       <c r="CK34" s="1">
         <v>5</v>
       </c>
+      <c r="CQ34" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR34" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS34" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT34" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU34" s="2">
+        <v>0</v>
+      </c>
+      <c r="CV34" s="2">
+        <v>0</v>
+      </c>
+      <c r="CW34" s="2">
+        <v>0</v>
+      </c>
+      <c r="CX34" s="2">
+        <v>0</v>
+      </c>
+      <c r="CY34" s="2">
+        <v>0</v>
+      </c>
+      <c r="CZ34" s="2">
+        <v>0</v>
+      </c>
+      <c r="DA34" s="2">
+        <v>0</v>
+      </c>
+      <c r="DB34" s="2">
+        <v>0</v>
+      </c>
+      <c r="DC34" s="2">
+        <v>0</v>
+      </c>
+      <c r="DD34" s="2">
+        <v>0</v>
+      </c>
+      <c r="DE34" s="2">
+        <v>0</v>
+      </c>
+      <c r="DF34" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG34" s="2">
+        <v>0</v>
+      </c>
+      <c r="DH34" s="2">
+        <v>0</v>
+      </c>
+      <c r="DI34" s="2">
+        <v>0</v>
+      </c>
+      <c r="DJ34" s="2">
+        <v>0</v>
+      </c>
       <c r="ET34" s="1">
         <v>0</v>
       </c>
@@ -4271,6 +4451,66 @@
       <c r="CJ35" s="1">
         <v>0</v>
       </c>
+      <c r="CQ35" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR35" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS35" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT35" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU35" s="2">
+        <v>0</v>
+      </c>
+      <c r="CV35" s="2">
+        <v>0</v>
+      </c>
+      <c r="CW35" s="2">
+        <v>0</v>
+      </c>
+      <c r="CX35" s="2">
+        <v>0</v>
+      </c>
+      <c r="CY35" s="2">
+        <v>0</v>
+      </c>
+      <c r="CZ35" s="2">
+        <v>0</v>
+      </c>
+      <c r="DA35" s="2">
+        <v>0</v>
+      </c>
+      <c r="DB35" s="2">
+        <v>0</v>
+      </c>
+      <c r="DC35" s="2">
+        <v>0</v>
+      </c>
+      <c r="DD35" s="2">
+        <v>0</v>
+      </c>
+      <c r="DE35" s="2">
+        <v>0</v>
+      </c>
+      <c r="DF35" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG35" s="2">
+        <v>0</v>
+      </c>
+      <c r="DH35" s="2">
+        <v>0</v>
+      </c>
+      <c r="DI35" s="2">
+        <v>0</v>
+      </c>
+      <c r="DJ35" s="2">
+        <v>0</v>
+      </c>
       <c r="ET35" s="1">
         <v>0</v>
       </c>
@@ -4294,6 +4534,66 @@
       <c r="CI36" s="1">
         <v>0</v>
       </c>
+      <c r="CQ36" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR36" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS36" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT36" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU36" s="2">
+        <v>0</v>
+      </c>
+      <c r="CV36" s="2">
+        <v>0</v>
+      </c>
+      <c r="CW36" s="2">
+        <v>0</v>
+      </c>
+      <c r="CX36" s="2">
+        <v>0</v>
+      </c>
+      <c r="CY36" s="2">
+        <v>0</v>
+      </c>
+      <c r="CZ36" s="2">
+        <v>0</v>
+      </c>
+      <c r="DA36" s="2">
+        <v>0</v>
+      </c>
+      <c r="DB36" s="2">
+        <v>0</v>
+      </c>
+      <c r="DC36" s="2">
+        <v>0</v>
+      </c>
+      <c r="DD36" s="2">
+        <v>0</v>
+      </c>
+      <c r="DE36" s="2">
+        <v>0</v>
+      </c>
+      <c r="DF36" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG36" s="2">
+        <v>0</v>
+      </c>
+      <c r="DH36" s="2">
+        <v>0</v>
+      </c>
+      <c r="DI36" s="2">
+        <v>0</v>
+      </c>
+      <c r="DJ36" s="2">
+        <v>0</v>
+      </c>
       <c r="ET36" s="1">
         <v>0</v>
       </c>
@@ -4317,6 +4617,66 @@
       <c r="CH37" s="1">
         <v>5</v>
       </c>
+      <c r="CQ37" s="2">
+        <v>0</v>
+      </c>
+      <c r="CR37" s="2">
+        <v>0</v>
+      </c>
+      <c r="CS37" s="2">
+        <v>0</v>
+      </c>
+      <c r="CT37" s="2">
+        <v>0</v>
+      </c>
+      <c r="CU37" s="2">
+        <v>0</v>
+      </c>
+      <c r="CV37" s="2">
+        <v>0</v>
+      </c>
+      <c r="CW37" s="2">
+        <v>0</v>
+      </c>
+      <c r="CX37" s="2">
+        <v>0</v>
+      </c>
+      <c r="CY37" s="2">
+        <v>0</v>
+      </c>
+      <c r="CZ37" s="2">
+        <v>0</v>
+      </c>
+      <c r="DA37" s="2">
+        <v>0</v>
+      </c>
+      <c r="DB37" s="2">
+        <v>0</v>
+      </c>
+      <c r="DC37" s="2">
+        <v>0</v>
+      </c>
+      <c r="DD37" s="2">
+        <v>0</v>
+      </c>
+      <c r="DE37" s="2">
+        <v>0</v>
+      </c>
+      <c r="DF37" s="2">
+        <v>0</v>
+      </c>
+      <c r="DG37" s="2">
+        <v>0</v>
+      </c>
+      <c r="DH37" s="2">
+        <v>0</v>
+      </c>
+      <c r="DI37" s="2">
+        <v>0</v>
+      </c>
+      <c r="DJ37" s="2">
+        <v>0</v>
+      </c>
       <c r="ET37" s="1">
         <v>0</v>
       </c>
@@ -4671,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="DA41" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="DB41" s="2">
         <v>0</v>
@@ -5157,7 +5517,7 @@
         <v>0</v>
       </c>
       <c r="DA47" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="DB47" s="2">
         <v>0</v>
@@ -5691,64 +6051,7 @@
       <c r="BZ52" s="4">
         <v>0</v>
       </c>
-      <c r="CQ52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CU52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CV52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CW52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CX52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CY52" s="2">
-        <v>0</v>
-      </c>
-      <c r="CZ52" s="2">
-        <v>0</v>
-      </c>
-      <c r="DA52" s="2">
-        <v>0</v>
-      </c>
-      <c r="DB52" s="2">
-        <v>0</v>
-      </c>
-      <c r="DC52" s="2">
-        <v>0</v>
-      </c>
-      <c r="DD52" s="2">
-        <v>0</v>
-      </c>
-      <c r="DE52" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF52" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG52" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH52" s="2">
-        <v>0</v>
-      </c>
-      <c r="DI52" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ52" s="2">
+      <c r="DF52" s="1">
         <v>0</v>
       </c>
       <c r="ET52" s="1">
@@ -5765,65 +6068,8 @@
       <c r="AP53" s="1">
         <v>5</v>
       </c>
-      <c r="CQ53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CU53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CV53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CW53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CX53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CY53" s="2">
-        <v>0</v>
-      </c>
-      <c r="CZ53" s="2">
-        <v>0</v>
-      </c>
-      <c r="DA53" s="2">
-        <v>0</v>
-      </c>
-      <c r="DB53" s="2">
-        <v>0</v>
-      </c>
-      <c r="DC53" s="2">
-        <v>0</v>
-      </c>
-      <c r="DD53" s="2">
-        <v>0</v>
-      </c>
-      <c r="DE53" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF53" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG53" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH53" s="2">
-        <v>0</v>
-      </c>
-      <c r="DI53" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ53" s="2">
-        <v>0</v>
+      <c r="DF53" s="1">
+        <v>4</v>
       </c>
       <c r="ET53" s="1">
         <v>0</v>
@@ -5839,64 +6085,7 @@
       <c r="AO54" s="1">
         <v>0</v>
       </c>
-      <c r="CQ54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CU54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CV54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CW54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CX54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CY54" s="2">
-        <v>0</v>
-      </c>
-      <c r="CZ54" s="2">
-        <v>0</v>
-      </c>
-      <c r="DA54" s="2">
-        <v>0</v>
-      </c>
-      <c r="DB54" s="2">
-        <v>0</v>
-      </c>
-      <c r="DC54" s="2">
-        <v>0</v>
-      </c>
-      <c r="DD54" s="2">
-        <v>0</v>
-      </c>
-      <c r="DE54" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF54" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG54" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH54" s="2">
-        <v>0</v>
-      </c>
-      <c r="DI54" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ54" s="2">
+      <c r="DF54" s="1">
         <v>0</v>
       </c>
       <c r="ET54" s="1">
@@ -5913,64 +6102,7 @@
       <c r="AO55" s="1">
         <v>0</v>
       </c>
-      <c r="CQ55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CU55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CV55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CW55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CX55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CY55" s="2">
-        <v>0</v>
-      </c>
-      <c r="CZ55" s="2">
-        <v>0</v>
-      </c>
-      <c r="DA55" s="2">
-        <v>0</v>
-      </c>
-      <c r="DB55" s="2">
-        <v>0</v>
-      </c>
-      <c r="DC55" s="2">
-        <v>0</v>
-      </c>
-      <c r="DD55" s="2">
-        <v>0</v>
-      </c>
-      <c r="DE55" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF55" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG55" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH55" s="2">
-        <v>0</v>
-      </c>
-      <c r="DI55" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ55" s="2">
+      <c r="DF55" s="1">
         <v>0</v>
       </c>
       <c r="ET55" s="1">
@@ -6002,65 +6134,8 @@
       <c r="AO56" s="1">
         <v>4</v>
       </c>
-      <c r="CQ56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CU56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CV56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CW56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CX56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CY56" s="2">
-        <v>0</v>
-      </c>
-      <c r="CZ56" s="2">
-        <v>0</v>
-      </c>
-      <c r="DA56" s="2">
-        <v>0</v>
-      </c>
-      <c r="DB56" s="2">
-        <v>0</v>
-      </c>
-      <c r="DC56" s="2">
-        <v>0</v>
-      </c>
-      <c r="DD56" s="2">
-        <v>0</v>
-      </c>
-      <c r="DE56" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF56" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG56" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH56" s="2">
-        <v>0</v>
-      </c>
-      <c r="DI56" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ56" s="2">
-        <v>0</v>
+      <c r="DF56" s="1">
+        <v>4</v>
       </c>
       <c r="ET56" s="1">
         <v>0</v>
@@ -6091,64 +6166,7 @@
       <c r="AO57" s="1">
         <v>0</v>
       </c>
-      <c r="CQ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CR57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CS57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CT57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CU57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CV57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CW57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CX57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CY57" s="2">
-        <v>0</v>
-      </c>
-      <c r="CZ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="DA57" s="2">
-        <v>0</v>
-      </c>
-      <c r="DB57" s="2">
-        <v>0</v>
-      </c>
-      <c r="DC57" s="2">
-        <v>0</v>
-      </c>
-      <c r="DD57" s="2">
-        <v>0</v>
-      </c>
-      <c r="DE57" s="2">
-        <v>0</v>
-      </c>
-      <c r="DF57" s="2">
-        <v>0</v>
-      </c>
-      <c r="DG57" s="2">
-        <v>0</v>
-      </c>
-      <c r="DH57" s="2">
-        <v>0</v>
-      </c>
-      <c r="DI57" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ57" s="2">
+      <c r="DF57" s="1">
         <v>0</v>
       </c>
       <c r="ET57" s="1">

--- a/media/Levels/Level_7.xlsx
+++ b/media/Levels/Level_7.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oyush\Desktop\勉強\DoctorRemote\DoctorRemote_α\media\Levels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D603D78-3AF2-4EC9-8852-E59B9BB50817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B17C905-3954-4CC7-8DD3-53FC8B601902}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D629F439-E2BD-4112-8312-753BDEB6F601}"/>
   </bookViews>
@@ -4205,6 +4205,9 @@
       <c r="CN32" s="1">
         <v>0</v>
       </c>
+      <c r="CP32" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ32" s="2">
         <v>0</v>
       </c>
@@ -4260,9 +4263,6 @@
         <v>0</v>
       </c>
       <c r="DI32" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ32" s="2">
         <v>0</v>
       </c>
       <c r="ET32" s="1">
@@ -4285,6 +4285,9 @@
       <c r="CL33" s="1">
         <v>0</v>
       </c>
+      <c r="CP33" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ33" s="2">
         <v>0</v>
       </c>
@@ -4340,9 +4343,6 @@
         <v>0</v>
       </c>
       <c r="DI33" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ33" s="2">
         <v>0</v>
       </c>
       <c r="ET33" s="1">
@@ -4368,6 +4368,9 @@
       <c r="CK34" s="1">
         <v>5</v>
       </c>
+      <c r="CP34" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ34" s="2">
         <v>0</v>
       </c>
@@ -4423,9 +4426,6 @@
         <v>0</v>
       </c>
       <c r="DI34" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ34" s="2">
         <v>0</v>
       </c>
       <c r="ET34" s="1">
@@ -4451,6 +4451,9 @@
       <c r="CJ35" s="1">
         <v>0</v>
       </c>
+      <c r="CP35" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ35" s="2">
         <v>0</v>
       </c>
@@ -4506,9 +4509,6 @@
         <v>0</v>
       </c>
       <c r="DI35" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ35" s="2">
         <v>0</v>
       </c>
       <c r="ET35" s="1">
@@ -4534,6 +4534,9 @@
       <c r="CI36" s="1">
         <v>0</v>
       </c>
+      <c r="CP36" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ36" s="2">
         <v>0</v>
       </c>
@@ -4589,9 +4592,6 @@
         <v>0</v>
       </c>
       <c r="DI36" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ36" s="2">
         <v>0</v>
       </c>
       <c r="ET36" s="1">
@@ -4617,6 +4617,9 @@
       <c r="CH37" s="1">
         <v>5</v>
       </c>
+      <c r="CP37" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ37" s="2">
         <v>0</v>
       </c>
@@ -4672,9 +4675,6 @@
         <v>0</v>
       </c>
       <c r="DI37" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ37" s="2">
         <v>0</v>
       </c>
       <c r="ET37" s="1">
@@ -4700,6 +4700,9 @@
       <c r="CG38" s="1">
         <v>0</v>
       </c>
+      <c r="CP38" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ38" s="2">
         <v>0</v>
       </c>
@@ -4755,9 +4758,6 @@
         <v>0</v>
       </c>
       <c r="DI38" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ38" s="2">
         <v>0</v>
       </c>
       <c r="ET38" s="1">
@@ -4909,9 +4909,6 @@
       <c r="DI39" s="2">
         <v>0</v>
       </c>
-      <c r="DJ39" s="2">
-        <v>0</v>
-      </c>
       <c r="ET39" s="1">
         <v>0</v>
       </c>
@@ -4926,6 +4923,9 @@
       <c r="AZ40" s="1">
         <v>5</v>
       </c>
+      <c r="CP40" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ40" s="2">
         <v>0</v>
       </c>
@@ -4981,9 +4981,6 @@
         <v>0</v>
       </c>
       <c r="DI40" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ40" s="2">
         <v>0</v>
       </c>
       <c r="ET40" s="1">
@@ -5000,6 +4997,9 @@
       <c r="AY41" s="1">
         <v>0</v>
       </c>
+      <c r="CP41" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ41" s="2">
         <v>0</v>
       </c>
@@ -5028,10 +5028,10 @@
         <v>0</v>
       </c>
       <c r="CZ41" s="2">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="DA41" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="DB41" s="2">
         <v>0</v>
@@ -5055,9 +5055,6 @@
         <v>0</v>
       </c>
       <c r="DI41" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ41" s="2">
         <v>0</v>
       </c>
       <c r="ET41" s="1">
@@ -5071,6 +5068,9 @@
       <c r="AX42" s="1">
         <v>0</v>
       </c>
+      <c r="CP42" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ42" s="2">
         <v>0</v>
       </c>
@@ -5126,9 +5126,6 @@
         <v>0</v>
       </c>
       <c r="DI42" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ42" s="2">
         <v>0</v>
       </c>
       <c r="ET42" s="1">
@@ -5142,6 +5139,9 @@
       <c r="AB43" s="1">
         <v>0</v>
       </c>
+      <c r="CP43" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ43" s="2">
         <v>0</v>
       </c>
@@ -5197,9 +5197,6 @@
         <v>0</v>
       </c>
       <c r="DI43" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ43" s="2">
         <v>0</v>
       </c>
       <c r="ET43" s="1">
@@ -5213,6 +5210,9 @@
       <c r="AC44" s="1">
         <v>6</v>
       </c>
+      <c r="CP44" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ44" s="2">
         <v>0</v>
       </c>
@@ -5268,9 +5268,6 @@
         <v>0</v>
       </c>
       <c r="DI44" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ44" s="2">
         <v>0</v>
       </c>
       <c r="ET44" s="1">
@@ -5284,6 +5281,9 @@
       <c r="AD45" s="1">
         <v>0</v>
       </c>
+      <c r="CP45" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ45" s="2">
         <v>0</v>
       </c>
@@ -5339,9 +5339,6 @@
         <v>0</v>
       </c>
       <c r="DI45" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ45" s="2">
         <v>0</v>
       </c>
       <c r="DR45" s="4">
@@ -5385,6 +5382,9 @@
       <c r="AE46" s="1">
         <v>0</v>
       </c>
+      <c r="CP46" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ46" s="2">
         <v>0</v>
       </c>
@@ -5440,9 +5440,6 @@
         <v>0</v>
       </c>
       <c r="DI46" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ46" s="2">
         <v>0</v>
       </c>
       <c r="DR46" s="4">
@@ -5486,6 +5483,9 @@
       <c r="AF47" s="1">
         <v>6</v>
       </c>
+      <c r="CP47" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ47" s="2">
         <v>0</v>
       </c>
@@ -5541,9 +5541,6 @@
         <v>0</v>
       </c>
       <c r="DI47" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ47" s="2">
         <v>0</v>
       </c>
       <c r="DR47" s="4">
@@ -5602,6 +5599,9 @@
       <c r="BZ48" s="4">
         <v>0</v>
       </c>
+      <c r="CP48" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ48" s="2">
         <v>0</v>
       </c>
@@ -5657,9 +5657,6 @@
         <v>0</v>
       </c>
       <c r="DI48" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ48" s="2">
         <v>0</v>
       </c>
       <c r="DR48" s="4">
@@ -5718,6 +5715,9 @@
       <c r="BZ49" s="4">
         <v>0</v>
       </c>
+      <c r="CP49" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ49" s="2">
         <v>0</v>
       </c>
@@ -5773,9 +5773,6 @@
         <v>0</v>
       </c>
       <c r="DI49" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ49" s="2">
         <v>0</v>
       </c>
       <c r="DR49" s="4">
@@ -5834,6 +5831,9 @@
       <c r="BZ50" s="4">
         <v>0</v>
       </c>
+      <c r="CP50" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ50" s="2">
         <v>0</v>
       </c>
@@ -5879,8 +5879,8 @@
       <c r="DE50" s="2">
         <v>0</v>
       </c>
-      <c r="DF50" s="2">
-        <v>0</v>
+      <c r="DF50" s="1">
+        <v>4</v>
       </c>
       <c r="DG50" s="2">
         <v>0</v>
@@ -5889,9 +5889,6 @@
         <v>0</v>
       </c>
       <c r="DI50" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ50" s="2">
         <v>0</v>
       </c>
       <c r="ET50" s="1">
@@ -5965,6 +5962,9 @@
       <c r="BZ51" s="4">
         <v>0</v>
       </c>
+      <c r="CP51" s="2">
+        <v>0</v>
+      </c>
       <c r="CQ51" s="2">
         <v>0</v>
       </c>
@@ -6010,7 +6010,7 @@
       <c r="DE51" s="2">
         <v>0</v>
       </c>
-      <c r="DF51" s="2">
+      <c r="DF51" s="1">
         <v>0</v>
       </c>
       <c r="DG51" s="2">
@@ -6020,9 +6020,6 @@
         <v>0</v>
       </c>
       <c r="DI51" s="2">
-        <v>0</v>
-      </c>
-      <c r="DJ51" s="2">
         <v>0</v>
       </c>
       <c r="ET51" s="1">
@@ -9293,8 +9290,8 @@
       <c r="J86" s="2">
         <v>0</v>
       </c>
-      <c r="K86" s="2">
-        <v>0</v>
+      <c r="K86" s="1">
+        <v>4</v>
       </c>
       <c r="L86" s="2">
         <v>0</v>
@@ -9385,7 +9382,7 @@
       <c r="J87" s="2">
         <v>0</v>
       </c>
-      <c r="K87" s="2">
+      <c r="K87" s="1">
         <v>0</v>
       </c>
       <c r="L87" s="2">
@@ -9398,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="O87" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P87" s="2">
         <v>0</v>
@@ -9525,7 +9522,7 @@
       <c r="J88" s="2">
         <v>0</v>
       </c>
-      <c r="K88" s="2">
+      <c r="K88" s="1">
         <v>0</v>
       </c>
       <c r="L88" s="2">
